--- a/laporan_padel_dki_jakarta_2026-10-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-16.xlsx
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.590.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp10.885.000</t>
+          <t>Rp11.385.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp1.790.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.898.000</t>
+          <t>Rp2.997.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.738.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.520.000</t>
+          <t>Rp6.620.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.666.000</t>
+          <t>Rp4.765.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.434.000</t>
+          <t>Rp3.734.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp9.415.000</t>
+          <t>Rp9.265.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp3.190.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.924.000</t>
+          <t>Rp7.422.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp9.980.000</t>
+          <t>Rp10.255.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp470.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp13.100.000</t>
+          <t>Rp13.302.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp21.250.000</t>
+          <t>Rp22.500.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp5.190.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp9.600.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.258.000</t>
+          <t>Rp6.582.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp476.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp27.125.000</t>
+          <t>Rp27.825.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>102</v>
       </c>
       <c r="D49" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp9.183.000</t>
+          <t>Rp9.412.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.295.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.649.993</t>
+          <t>Rp3.774.993</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp2.935.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.860.000</t>
+          <t>Rp3.395.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.873.000</t>
+          <t>Rp3.071.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.885.000</t>
+          <t>Rp5.480.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-16.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.020.000</t>
+          <t>Rp2.180.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.100.000</t>
+          <t>Rp11.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.972.988</t>
+          <t>Rp7.141.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.785.000</t>
+          <t>Rp7.115.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.060.500</t>
+          <t>Rp12.335.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.590.000</t>
+          <t>Rp3.090.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp11.385.000</t>
+          <t>Rp12.125.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.819.000</t>
+          <t>Rp14.217.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.189.000</t>
+          <t>Rp1.439.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.760.000</t>
+          <t>Rp3.480.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.997.000</t>
+          <t>Rp3.177.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.738.000</t>
+          <t>Rp3.092.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp2.055.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.236.000</t>
+          <t>Rp5.936.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>28</v>
       </c>
       <c r="D49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp620.000</t>
+          <t>Rp310.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>32</v>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp597.000</t>
+          <t>Rp672.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.620.000</t>
+          <t>Rp7.060.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.148.000</t>
+          <t>Rp1.247.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.165.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.660.000</t>
+          <t>Rp2.795.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.870.000</t>
+          <t>Rp3.410.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.240.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>108</v>
       </c>
       <c r="D85" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp2.460.000</t>
+          <t>Rp2.940.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.090.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp5.421.000</t>
+          <t>Rp6.117.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp1.720.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.850.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.305.000</t>
+          <t>Rp3.355.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.770.000</t>
+          <t>Rp7.560.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.770.000</t>
+          <t>Rp5.580.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.715.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp22.000.000</t>
+          <t>Rp22.150.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.999.000</t>
+          <t>Rp4.399.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp275.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp7.575.000</t>
+          <t>Rp7.825.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp124.000</t>
+          <t>Rp266.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp10.200.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp4.380.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp35.400.000</t>
+          <t>Rp36.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.996.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp16.470.000</t>
+          <t>Rp17.030.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.165.000</t>
+          <t>Rp11.390.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.011.000</t>
+          <t>Rp1.149.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.325.000</t>
+          <t>Rp14.600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.361.000</t>
+          <t>Rp18.201.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.710.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.498.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.305.000</t>
+          <t>Rp5.580.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.942.000</t>
+          <t>Rp4.342.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.900.000</t>
+          <t>Rp20.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.582.000</t>
+          <t>Rp5.918.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp419.000</t>
+          <t>Rp579.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.590.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp3.970.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp13.600.000</t>
+          <t>Rp16.325.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp27.825.000</t>
+          <t>Rp29.125.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp4.270.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.245.000</t>
+          <t>Rp1.615.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.035.000</t>
+          <t>Rp12.455.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.440.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp6.477.000</t>
+          <t>Rp6.178.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.605.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.970.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp7.315.000</t>
+          <t>Rp6.015.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.880.000</t>
+          <t>Rp19.840.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.410.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.935.000</t>
+          <t>Rp3.130.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.071.000</t>
+          <t>Rp3.121.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.984.000</t>
+          <t>Rp2.491.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.475.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-16.xlsx
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.514.000</t>
+          <t>Rp1.784.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.141.988</t>
+          <t>Rp5.745.992</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.115.000</t>
+          <t>Rp7.615.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.335.500</t>
+          <t>Rp11.969.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.090.000</t>
+          <t>Rp3.510.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp888.000</t>
+          <t>Rp1.107.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp790.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.480.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.048.000</t>
+          <t>Rp3.258.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.177.000</t>
+          <t>Rp3.456.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.535.000</t>
+          <t>Rp4.155.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.670.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.936.000</t>
+          <t>Rp6.136.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp890.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp216.000</t>
+          <t>Rp312.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp1.670.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp7.060.000</t>
+          <t>Rp7.260.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp3.120.000</t>
+          <t>Rp3.440.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.486.000</t>
+          <t>Rp5.284.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.247.000</t>
+          <t>Rp1.346.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.190.000</t>
+          <t>Rp1.692.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp2.315.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.795.000</t>
+          <t>Rp3.835.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.410.000</t>
+          <t>Rp3.810.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.240.000</t>
+          <t>Rp6.630.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.765.000</t>
+          <t>Rp5.063.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp1.841.000</t>
+          <t>Rp3.086.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.225.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp6.117.000</t>
+          <t>Rp5.619.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.555.000</t>
+          <t>Rp4.355.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.458.000</t>
+          <t>Rp1.539.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.060.000</t>
+          <t>Rp4.255.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp12.500.000</t>
+          <t>Rp12.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp7.422.000</t>
+          <t>Rp8.020.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.975.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.845.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp7.825.000</t>
+          <t>Rp8.525.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.675.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.100.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp266.000</t>
+          <t>Rp337.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp470.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp3.045.000</t>
+          <t>Rp3.605.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp9.300.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp11.450.000</t>
+          <t>Rp12.450.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp22.500.000</t>
+          <t>Rp24.400.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp9.050.000</t>
+          <t>Rp10.800.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.365.000</t>
+          <t>Rp15.400.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.350.000</t>
+          <t>Rp11.450.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp36.400.000</t>
+          <t>Rp38.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.351.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp6.290.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.996.000</t>
+          <t>Rp2.996.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6441,7 +6441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp17.030.000</t>
+          <t>Rp17.770.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.600.000</t>
+          <t>Rp15.100.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.687.000</t>
+          <t>Rp9.036.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp4.040.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.498.000</t>
+          <t>Rp2.614.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.580.000</t>
+          <t>Rp6.040.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.342.000</t>
+          <t>Rp4.542.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.234.000</t>
+          <t>Rp3.503.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.500.000</t>
+          <t>Rp20.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.918.000</t>
+          <t>Rp4.985.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7169,28 +7169,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VIP Padel MK</t>
+          <t>Portside Padel Club</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp579.000</t>
+          <t>Rp3.315.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp260.000</t>
+          <t>Rp150.000 - Rp255.000</t>
         </is>
       </c>
     </row>
@@ -7200,28 +7200,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>My Club House - Padel</t>
+          <t>VIP Padel MK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.110.000</t>
+          <t>Rp1.099.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp170.000 - Rp250.000</t>
+          <t>Rp99.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -7231,28 +7231,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MSC Padel Sunter</t>
+          <t>My Club House - Padel</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.590.000</t>
+          <t>Rp5.110.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp175.000</t>
+          <t>Rp170.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7262,28 +7262,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Heliix Padel</t>
+          <t>MSC Padel Sunter</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp1.590.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp50.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7293,28 +7293,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Garuda Padel Club</t>
+          <t>Heliix Padel</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp275.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cometa Padel VIP Lounge</t>
+          <t>Garuda Padel Club</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.240.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp1.000.000</t>
+          <t>Rp150.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7355,28 +7355,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nordic Courts</t>
+          <t>Cometa Padel VIP Lounge</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.853.000</t>
+          <t>Rp6.570.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp77.000 - Rp250.000</t>
+          <t>Rp70.000 - Rp1.000.000</t>
         </is>
       </c>
     </row>
@@ -7386,28 +7386,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Padel Go Blast</t>
+          <t>Nordic Courts</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.853.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp90.000 - Rp175.000</t>
+          <t>Rp77.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7417,28 +7417,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Padel Commons</t>
+          <t>Padel Go Blast</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.970.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp285.000</t>
+          <t>Rp90.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7448,28 +7448,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bandeja Padel Arena</t>
+          <t>Padel Commons</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp8.265.000</t>
+          <t>Rp4.145.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp245.000</t>
+          <t>Rp125.000 - Rp285.000</t>
         </is>
       </c>
     </row>
@@ -7479,28 +7479,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fivestar Signature Club</t>
+          <t>Bandeja Padel Arena</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp16.325.000</t>
+          <t>Rp8.265.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp500.000</t>
+          <t>Rp195.000 - Rp245.000</t>
         </is>
       </c>
     </row>
@@ -7510,28 +7510,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rivera Padel Pluit</t>
+          <t>Fivestar Signature Club</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp17.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp348.000</t>
+          <t>Rp50.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -7541,28 +7541,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Happy Padel Place</t>
+          <t>Rivera Padel Pluit</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.764.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp285.000</t>
+          <t>Rp100.000 - Rp348.000</t>
         </is>
       </c>
     </row>
@@ -7572,28 +7572,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>X3 Padel</t>
+          <t>Happy Padel Place</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp3.533.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp200.000</t>
+          <t>Rp149.000 - Rp285.000</t>
         </is>
       </c>
     </row>
@@ -7603,28 +7603,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Club House Padel - Pantai Mutiara Pluit</t>
+          <t>X3 Padel</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp476.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp188.000 - Rp288.000</t>
+          <t>Rp50.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -7634,28 +7634,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Staple Social Club</t>
+          <t>The Club House Padel - Pantai Mutiara Pluit</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp476.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp188.000 - Rp288.000</t>
         </is>
       </c>
     </row>
@@ -7665,28 +7665,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pluit Padel Parq (PPP)</t>
+          <t>Staple Social Club</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp29.125.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp425.000</t>
+          <t>Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7696,28 +7696,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nord Social Club</t>
+          <t>Pluit Padel Parq (PPP)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp6.799.000</t>
+          <t>Rp29.125.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp350.000 - Rp599.000</t>
+          <t>Rp200.000 - Rp425.000</t>
         </is>
       </c>
     </row>
@@ -7727,28 +7727,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Genesis Padel Club</t>
+          <t>Nord Social Club</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.199.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp250.000</t>
+          <t>Rp350.000 - Rp599.000</t>
         </is>
       </c>
     </row>
@@ -7758,28 +7758,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Padel Guru JIS</t>
+          <t>Genesis Padel Club</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp4.775.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp200.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7789,28 +7789,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gading Mas Racquet Club</t>
+          <t>Padel Guru JIS</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.775.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp110.000 - Rp275.000</t>
+          <t>Rp180.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -7820,28 +7820,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YOLO Sports &amp; Lifestyle Pluit</t>
+          <t>Gading Mas Racquet Club</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp24.025.000</t>
+          <t>Rp10.775.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp700.000</t>
+          <t>Rp110.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7851,28 +7851,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Foreground Racquet Simulator - Pluit</t>
+          <t>YOLO Sports &amp; Lifestyle Pluit</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp860.000</t>
+          <t>Rp24.025.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp205.000 - Rp225.000</t>
+          <t>Rp150.000 - Rp700.000</t>
         </is>
       </c>
     </row>
@@ -7882,28 +7882,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Raquette Temple Sunter</t>
+          <t>Foreground Racquet Simulator - Pluit</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp1.310.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp400.000</t>
+          <t>Rp205.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -7913,28 +7913,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Foreground  Racquet Simulator - Sunter</t>
+          <t>The Raquette Temple Sunter</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp275.000</t>
+          <t>Rp250.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -7944,28 +7944,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>House of Mayor</t>
+          <t>Foreground  Racquet Simulator - Sunter</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp9.412.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp229.000 - Rp349.000</t>
+          <t>Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7975,28 +7975,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Let's Go Padel Sunter</t>
+          <t>House of Mayor</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp8.710.000</t>
+          <t>Rp8.016.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp350.000</t>
+          <t>Rp229.000 - Rp349.000</t>
         </is>
       </c>
     </row>
@@ -8006,28 +8006,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Padre Padel Kelapa Gading</t>
+          <t>Let's Go Padel Sunter</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp8.710.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp175.000</t>
+          <t>Rp150.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -8037,26 +8037,57 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>Padre Padel Kelapa Gading</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>144</v>
+      </c>
+      <c r="D52" t="n">
+        <v>104</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rp6.750.000</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rp125.000 - Rp175.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>wePADL at Meridian Sports &amp; Wellness (MSW) PIK</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C53" t="n">
         <v>90</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D53" t="n">
         <v>67</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>25.6%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Rp5.200.000</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Rp75.000 - Rp300.000</t>
         </is>
@@ -8126,16 +8157,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.615.000</t>
+          <t>Rp1.765.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8188,16 +8219,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.260.000</t>
+          <t>Rp2.780.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8250,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp6.178.000</t>
+          <t>Rp5.580.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8281,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.730.000</t>
+          <t>Rp4.670.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8312,16 +8343,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.665.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8529,16 +8560,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.649.993</t>
+          <t>Rp3.849.992</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8715,16 +8746,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.840.000</t>
+          <t>Rp21.280.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8808,16 +8839,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.770.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8870,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.774.993</t>
+          <t>Rp4.174.991</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8901,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp4.315.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8994,16 +9025,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9118,16 +9149,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.130.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9149,16 +9180,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.395.000</t>
+          <t>Rp3.160.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9180,16 +9211,16 @@
         <v>128</v>
       </c>
       <c r="D36" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.627.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9273,16 +9304,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.480.000</t>
+          <t>Rp4.530.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9304,16 +9335,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.491.000</t>
+          <t>Rp2.829.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-16.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.292.000</t>
+          <t>Rp2.592.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.969.000</t>
+          <t>Rp12.519.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp790.000</t>
+          <t>Rp915.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.258.000</t>
+          <t>Rp3.177.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.060.000</t>
+          <t>Rp6.310.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp1.830.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.055.000</t>
+          <t>Rp2.445.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp60.000</t>
+          <t>Rp210.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp4.620.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp5.063.000</t>
+          <t>Rp5.163.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.679.000</t>
+          <t>Rp2.977.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp5.619.000</t>
+          <t>Rp5.868.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.720.000</t>
+          <t>Rp1.945.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.580.000</t>
+          <t>Rp2.385.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.410.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.675.000</t>
+          <t>Rp6.850.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.336.000</t>
+          <t>Rp6.732.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp337.000</t>
+          <t>Rp390.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp13.302.000</t>
+          <t>Rp13.500.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.450.000</t>
+          <t>Rp12.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp38.800.000</t>
+          <t>Rp37.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp17.770.000</t>
+          <t>Rp17.130.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.614.000</t>
+          <t>Rp3.730.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.584.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.985.000</t>
+          <t>Rp5.322.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.145.000</t>
+          <t>Rp3.735.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp8.265.000</t>
+          <t>Rp8.705.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp29.125.000</t>
+          <t>Rp29.475.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp5.199.000</t>
+          <t>Rp5.999.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp24.025.000</t>
+          <t>Rp24.475.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp8.710.000</t>
+          <t>Rp9.390.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.075.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.440.000</t>
+          <t>Rp6.140.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.280.000</t>
+          <t>Rp21.760.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp570.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-16.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-16.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.180.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.592.000</t>
+          <t>Rp2.742.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp915.000</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.720.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.830.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.977.000</t>
+          <t>Rp3.076.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp4.355.000</t>
+          <t>Rp4.595.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.690.500</t>
+          <t>Rp17.030.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.410.000</t>
+          <t>Rp3.235.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.399.000</t>
+          <t>Rp4.699.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp3.605.000</t>
+          <t>Rp3.955.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp13.500.000</t>
+          <t>Rp13.676.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp24.400.000</t>
+          <t>Rp24.750.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.400.000</t>
+          <t>Rp13.090.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp37.200.000</t>
+          <t>Rp37.550.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.290.000</t>
+          <t>Rp6.410.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp17.130.000</t>
+          <t>Rp17.210.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.040.000</t>
+          <t>Rp4.440.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.800.000</t>
+          <t>Rp21.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp8.705.000</t>
+          <t>Rp9.095.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.050.000</t>
+          <t>Rp17.600.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.533.000</t>
+          <t>Rp3.931.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.455.000</t>
+          <t>Rp12.705.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.315.000</t>
+          <t>Rp4.530.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp3.310.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>128</v>
       </c>
       <c r="D36" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.524.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.530.000</t>
+          <t>Rp4.680.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
